--- a/invoices/invoice_2026-04-05.xlsx
+++ b/invoices/invoice_2026-04-05.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>PT MITRA BISNIS Indonesia</t>
+          <t>UD BERKAH JAYA</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Jl. Gatot Subroto No. 999, Bandung 40123</t>
+          <t>Jl. Raya Bogor No. 88, Depok 16413</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Budi Santoso | budi@mitraindonesia.com</t>
+          <t>Hendra Putra | hendra@berkahjaya.id</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Software Development</t>
+          <t>Technical Documentation</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>5000000</v>
+        <v>250000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -714,14 +714,14 @@
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Setup</t>
+          <t>UI/UX Design Services</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>1200000</v>
+        <v>750000</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>0.11</v>
@@ -734,14 +734,14 @@
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>QA &amp; Testing Services</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>0.11</v>
@@ -809,15 +809,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B28:F28"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/invoices/invoice_2026-04-05.xlsx
+++ b/invoices/invoice_2026-04-05.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PAID</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>UD BERKAH JAYA</t>
+          <t>PT MITRA BISNIS Indonesia</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Jl. Raya Bogor No. 88, Depok 16413</t>
+          <t>Jl. Gatot Subroto No. 999, Bandung 40123</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Hendra Putra | hendra@berkahjaya.id</t>
+          <t>Budi Santoso | budi@mitraindonesia.com</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>Project Management</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>250000</v>
+        <v>450000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>750000</v>
@@ -734,14 +734,14 @@
     <row r="18" ht="28" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>QA &amp; Testing Services</t>
+          <t>API Development</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>350000</v>
+        <v>900000</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>0.11</v>
